--- a/dev/12.2.1.xlsx
+++ b/dev/12.2.1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jeremiah Goates\git-repos\Flight_Sim\dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33AB5181-F76F-42B5-A5FB-8CF0DF71A7EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B61DB04A-25CC-4CC8-B882-FCF4AA2C5CED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{449B0D0B-F1CC-44A4-9497-F7B37413503A}"/>
   </bookViews>
@@ -347,8 +347,17 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -359,16 +368,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -17787,140 +17787,140 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:39" x14ac:dyDescent="0.25">
-      <c r="H2" s="16" t="s">
+      <c r="H2" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="M2" s="16" t="s">
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="M2" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="N2" s="21"/>
-      <c r="O2" s="21"/>
-      <c r="P2" s="21"/>
-      <c r="Q2" s="21"/>
-      <c r="R2" s="21"/>
-      <c r="S2" s="21"/>
-      <c r="U2" s="16" t="s">
+      <c r="N2" s="23"/>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
+      <c r="S2" s="23"/>
+      <c r="U2" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="V2" s="21"/>
-      <c r="W2" s="21"/>
-      <c r="X2" s="21"/>
-      <c r="Y2" s="21"/>
-      <c r="Z2" s="21"/>
-      <c r="AA2" s="21"/>
+      <c r="V2" s="23"/>
+      <c r="W2" s="23"/>
+      <c r="X2" s="23"/>
+      <c r="Y2" s="23"/>
+      <c r="Z2" s="23"/>
+      <c r="AA2" s="23"/>
     </row>
     <row r="3" spans="2:39" x14ac:dyDescent="0.25">
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="H3" s="16"/>
-      <c r="I3" s="16"/>
-      <c r="J3" s="16"/>
-      <c r="K3" s="16"/>
-      <c r="M3" s="21"/>
-      <c r="N3" s="21"/>
-      <c r="O3" s="21"/>
-      <c r="P3" s="21"/>
-      <c r="Q3" s="21"/>
-      <c r="R3" s="21"/>
-      <c r="S3" s="21"/>
-      <c r="U3" s="21"/>
-      <c r="V3" s="21"/>
-      <c r="W3" s="21"/>
-      <c r="X3" s="21"/>
-      <c r="Y3" s="21"/>
-      <c r="Z3" s="21"/>
-      <c r="AA3" s="21"/>
-      <c r="AC3" s="16" t="s">
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
+      <c r="M3" s="23"/>
+      <c r="N3" s="23"/>
+      <c r="O3" s="23"/>
+      <c r="P3" s="23"/>
+      <c r="Q3" s="23"/>
+      <c r="R3" s="23"/>
+      <c r="S3" s="23"/>
+      <c r="U3" s="23"/>
+      <c r="V3" s="23"/>
+      <c r="W3" s="23"/>
+      <c r="X3" s="23"/>
+      <c r="Y3" s="23"/>
+      <c r="Z3" s="23"/>
+      <c r="AA3" s="23"/>
+      <c r="AC3" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="AD3" s="16"/>
-      <c r="AE3" s="16"/>
-      <c r="AF3" s="16"/>
-      <c r="AG3" s="16"/>
-      <c r="AH3" s="16"/>
-      <c r="AI3" s="16"/>
-      <c r="AJ3" s="16"/>
-      <c r="AK3" s="16"/>
-      <c r="AL3" s="16"/>
-      <c r="AM3" s="16"/>
+      <c r="AD3" s="17"/>
+      <c r="AE3" s="17"/>
+      <c r="AF3" s="17"/>
+      <c r="AG3" s="17"/>
+      <c r="AH3" s="17"/>
+      <c r="AI3" s="17"/>
+      <c r="AJ3" s="17"/>
+      <c r="AK3" s="17"/>
+      <c r="AL3" s="17"/>
+      <c r="AM3" s="17"/>
     </row>
     <row r="4" spans="2:39" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="H4" s="17" t="s">
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="H4" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="18" t="s">
+      <c r="I4" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="J4" s="18" t="s">
+      <c r="J4" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="K4" s="18" t="s">
+      <c r="K4" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="M4" s="17" t="s">
+      <c r="M4" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="N4" s="18" t="s">
+      <c r="N4" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="O4" s="20" t="s">
+      <c r="O4" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="P4" s="20" t="s">
+      <c r="P4" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="Q4" s="20" t="s">
+      <c r="Q4" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="R4" s="19" t="s">
+      <c r="R4" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="S4" s="20" t="s">
+      <c r="S4" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="U4" s="17" t="s">
+      <c r="U4" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="V4" s="18" t="s">
+      <c r="V4" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="W4" s="20" t="s">
+      <c r="W4" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="X4" s="20" t="s">
+      <c r="X4" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="Y4" s="20" t="s">
+      <c r="Y4" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="Z4" s="19" t="s">
+      <c r="Z4" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="AA4" s="19" t="s">
+      <c r="AA4" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="AC4" s="16"/>
-      <c r="AD4" s="16"/>
-      <c r="AE4" s="16"/>
-      <c r="AF4" s="16"/>
-      <c r="AG4" s="16"/>
-      <c r="AH4" s="16"/>
-      <c r="AI4" s="16"/>
-      <c r="AJ4" s="16"/>
-      <c r="AK4" s="16"/>
-      <c r="AL4" s="16"/>
-      <c r="AM4" s="16"/>
+      <c r="AC4" s="17"/>
+      <c r="AD4" s="17"/>
+      <c r="AE4" s="17"/>
+      <c r="AF4" s="17"/>
+      <c r="AG4" s="17"/>
+      <c r="AH4" s="17"/>
+      <c r="AI4" s="17"/>
+      <c r="AJ4" s="17"/>
+      <c r="AK4" s="17"/>
+      <c r="AL4" s="17"/>
+      <c r="AM4" s="17"/>
     </row>
     <row r="5" spans="2:39" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
@@ -17935,24 +17935,24 @@
       <c r="E5" s="5">
         <v>350</v>
       </c>
-      <c r="H5" s="17"/>
-      <c r="I5" s="18"/>
-      <c r="J5" s="18"/>
-      <c r="K5" s="18"/>
-      <c r="M5" s="17"/>
-      <c r="N5" s="18"/>
-      <c r="O5" s="20"/>
-      <c r="P5" s="20"/>
-      <c r="Q5" s="20"/>
-      <c r="R5" s="19"/>
-      <c r="S5" s="20"/>
-      <c r="U5" s="17"/>
-      <c r="V5" s="18"/>
-      <c r="W5" s="20"/>
-      <c r="X5" s="20"/>
-      <c r="Y5" s="20"/>
-      <c r="Z5" s="19"/>
-      <c r="AA5" s="19"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="21"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="21"/>
+      <c r="M5" s="20"/>
+      <c r="N5" s="21"/>
+      <c r="O5" s="16"/>
+      <c r="P5" s="16"/>
+      <c r="Q5" s="16"/>
+      <c r="R5" s="22"/>
+      <c r="S5" s="16"/>
+      <c r="U5" s="20"/>
+      <c r="V5" s="21"/>
+      <c r="W5" s="16"/>
+      <c r="X5" s="16"/>
+      <c r="Y5" s="16"/>
+      <c r="Z5" s="22"/>
+      <c r="AA5" s="22"/>
     </row>
     <row r="6" spans="2:39" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
@@ -18483,7 +18483,7 @@
         <v>94.022923887505627</v>
       </c>
       <c r="P12">
-        <f t="shared" si="10"/>
+        <f>IF(ABS(S11)&gt;21, P11, P11+(O12+O11)*$E$8/2)</f>
         <v>0</v>
       </c>
       <c r="Q12">
@@ -18757,12 +18757,12 @@
       </c>
     </row>
     <row r="16" spans="2:39" x14ac:dyDescent="0.25">
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
       <c r="H16" s="15">
         <f t="shared" si="7"/>
         <v>9.9999999999999992E-2</v>
@@ -18837,10 +18837,10 @@
       </c>
     </row>
     <row r="17" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="16"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
       <c r="H17" s="15">
         <f t="shared" si="7"/>
         <v>0.10999999999999999</v>
@@ -19927,10 +19927,10 @@
       </c>
     </row>
     <row r="31" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B31" s="22" t="s">
+      <c r="B31" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="C31" s="22"/>
+      <c r="C31" s="19"/>
       <c r="H31" s="15">
         <f t="shared" si="7"/>
         <v>0.25000000000000006</v>
@@ -20005,8 +20005,8 @@
       </c>
     </row>
     <row r="32" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B32" s="22"/>
-      <c r="C32" s="22"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
       <c r="H32" s="15">
         <f t="shared" si="7"/>
         <v>0.26000000000000006</v>
@@ -40400,15 +40400,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="Q4:Q5"/>
-    <mergeCell ref="S4:S5"/>
-    <mergeCell ref="B3:E4"/>
-    <mergeCell ref="B16:E17"/>
-    <mergeCell ref="B31:C32"/>
-    <mergeCell ref="M4:M5"/>
-    <mergeCell ref="N4:N5"/>
-    <mergeCell ref="O4:O5"/>
-    <mergeCell ref="P4:P5"/>
     <mergeCell ref="AC3:AM4"/>
     <mergeCell ref="H2:K3"/>
     <mergeCell ref="H4:H5"/>
@@ -40425,6 +40416,15 @@
     <mergeCell ref="Z4:Z5"/>
     <mergeCell ref="AA4:AA5"/>
     <mergeCell ref="M2:S3"/>
+    <mergeCell ref="Q4:Q5"/>
+    <mergeCell ref="S4:S5"/>
+    <mergeCell ref="B3:E4"/>
+    <mergeCell ref="B16:E17"/>
+    <mergeCell ref="B31:C32"/>
+    <mergeCell ref="M4:M5"/>
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="O4:O5"/>
+    <mergeCell ref="P4:P5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
